--- a/TIMES-NZ/v303/SubRES_TMPL/SubRES_NewTechs_AGR_Transformation.xlsx
+++ b/TIMES-NZ/v303/SubRES_TMPL/SubRES_NewTechs_AGR_Transformation.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob-Bike-PET</t>
+          <t>ALIVE-MoTP-Mob-Bike-ELC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob-Bike-ELC</t>
+          <t>AHORT-MoTP-Mob-Trac-ELC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-Trac-ELC</t>
+          <t>AHORT-MoTP-Mob-Trac-H2R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-Trac-H2R</t>
+          <t>AHORT-MoTP-Mob-MTr-ELC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-MTr-ELC</t>
+          <t>AHORT-MoTP-Mob-MTr-H2R</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-MTr-H2R</t>
+          <t>AHORT-MoTP-Mob-Uti-ELC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-Uti-ELC</t>
+          <t>AHORT-MoTP-Mob-Uti-H2R</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-Uti-H2R</t>
+          <t>AHORT-MoTP-Stat-Motor-ELC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Stat-Motor-ELC</t>
+          <t>AINDC-SH-Boiler-WOD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AINDC-SH-Boiler-WOD</t>
+          <t>AINDC-SH-Boiler-ELC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AINDC-SH-Boiler-ELC</t>
+          <t>AINDC-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AINDC-SH-Boiler-H2R</t>
+          <t>AINDC-SH-HP-ELC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AINDC-SH-HP-ELC</t>
+          <t>AFORE-MoTP-Mob-GB-ELC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob-GB-ELC</t>
+          <t>AFORE-MoTP-Mob-GB-H2R</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob-GB-H2R</t>
+          <t>AFORE-MoTP-Mob-CY-ELC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob-CY-ELC</t>
+          <t>AFORE-MoTP-Mob-CY-H2R</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob-CY-H2R</t>
+          <t>AFORE-MoTP-Mob-Bike-ELC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1279,128 +1279,163 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>DMD</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>AFISH-MoTP-Mob-HYBBoat-DSL</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>GW</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>DAYNITE</t>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>AgricultureNewTechParameters</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>Defines technical parameters for future ag, forest, fish technologies</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>AgricultureNewTechParameters</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>Defines technical parameters for future ag, forest, fish technologies</t>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>~FI_T</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>~FI_T</t>
+          <t>TechName</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Comm-In</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Comm-Out</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>EFF</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>INVCOST</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>INVCOST~2030</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>INVCOST~2050</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>FIXOM</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>AF</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CAP2ACT</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TechName</t>
+          <t>ADCF-MoTP-Mob-Trac-ELC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Comm-In</t>
+          <t>AGRELC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Comm-Out</t>
+          <t>ADCF-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>START</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EFF</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>INVCOST</t>
+          <t>3779.418907487805</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>INVCOST~2030</t>
+          <t>1595.220724</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INVCOST~2050</t>
+          <t>1071.7594</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>FIXOM</t>
+          <t>70.1002295492195</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>AF</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CAP2ACT</t>
+          <t>31.536</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob-Trac-ELC</t>
+          <t>ADCF-MoTP-Mob-Trac-H2R</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AGRELC</t>
+          <t>AGRH2R</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1410,7 +1445,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1420,22 +1455,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3779.418907487805</t>
+          <t>2833.988416271219</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1595.220724</t>
+          <t>2140.786796</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1071.7594</t>
+          <t>675.3559438</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>70.1002295492195</t>
+          <t>42.683891665814635</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -1452,17 +1487,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob-Trac-H2R</t>
+          <t>ADCF-MoTP-Mob-MTr-ELC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AGRH2R</t>
+          <t>AGRELC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1472,37 +1507,37 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2833.988416271219</t>
+          <t>8063.7538839102435</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2140.786796</t>
+          <t>2084.875383</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>675.3559438</t>
+          <t>2084.875383</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>42.683891665814635</t>
+          <t>80.37697446720975</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -1514,17 +1549,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob-MTr-ELC</t>
+          <t>ADCF-MoTP-Mob-MTr-H2R</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AGRELC</t>
+          <t>AGRH2R</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1534,7 +1569,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1544,22 +1579,22 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8063.7538839102435</t>
+          <t>9263.961875734634</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2084.875383</t>
+          <t>3104.0294</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2084.875383</t>
+          <t>2501.400538</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>80.37697446720975</t>
+          <t>87.63041650479023</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -1576,17 +1611,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob-MTr-H2R</t>
+          <t>ADCF-MoTP-Mob-Uti-ELC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AGRH2R</t>
+          <t>AGRELC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1596,7 +1631,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1606,27 +1641,27 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>9263.961875734634</t>
+          <t>691.8727024390244</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3104.0294</t>
+          <t>413.47</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2501.400538</t>
+          <t>413.47</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>87.63041650479023</t>
+          <t>12.933898883882927</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -1638,17 +1673,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob-Uti-ELC</t>
+          <t>ADCF-MoTP-Mob-Uti-H2R</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AGRELC</t>
+          <t>AGRH2R</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1658,7 +1693,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1668,22 +1703,22 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>691.8727024390244</t>
+          <t>919.5735999999999</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>413.47</t>
+          <t>431.38</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>413.47</t>
+          <t>408.55</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>12.933898883882927</t>
+          <t>16.042381847453658</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -1700,17 +1735,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob-Uti-H2R</t>
+          <t>ADCF-MoTP-Mob-Bike-ELC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AGRH2R</t>
+          <t>AGRELC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-Bike-MoTP-Mob</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1720,37 +1755,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>919.5735999999999</t>
+          <t>593.2653658536585</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>431.38</t>
+          <t>287.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>408.55</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>16.042381847453658</t>
+          <t>307.0731707317073</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -1762,7 +1797,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob-Bike-ELC</t>
+          <t>ALIVE-MoTP-Mob-Trac-ELC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1772,7 +1807,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ALIVE-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1782,37 +1817,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.386473</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>593.2653658536585</t>
+          <t>3779.418907487805</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>287.0</t>
+          <t>1595.220724</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>1071.7594</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>307.0731707317073</t>
+          <t>70.1002295492195</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -1824,17 +1859,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob-Trac-ELC</t>
+          <t>ALIVE-MoTP-Mob-Trac-H2R</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AGRELC</t>
+          <t>AGRH2R</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob</t>
+          <t>ALIVE-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1844,7 +1879,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.386473</t>
+          <t>0.241546</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1854,22 +1889,22 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3779.418907487805</t>
+          <t>2833.988416271219</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1595.220724</t>
+          <t>2140.786796</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1071.7594</t>
+          <t>675.3559438</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>70.1002295492195</t>
+          <t>42.683891665814635</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -1886,17 +1921,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob-Trac-H2R</t>
+          <t>ALIVE-MoTP-Mob-MTr-ELC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AGRH2R</t>
+          <t>AGRELC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob</t>
+          <t>ALIVE-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1906,37 +1941,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.241546</t>
+          <t>0.43535</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2833.988416271219</t>
+          <t>8063.7538839102435</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2140.786796</t>
+          <t>2084.875383</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>675.3559438</t>
+          <t>2084.875383</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>42.683891665814635</t>
+          <t>80.37697446720975</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -1948,17 +1983,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob-MTr-ELC</t>
+          <t>ALIVE-MoTP-Mob-MTr-H2R</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AGRELC</t>
+          <t>AGRH2R</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob</t>
+          <t>ALIVE-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1968,7 +2003,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.43535</t>
+          <t>0.272093</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1978,22 +2013,22 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8063.7538839102435</t>
+          <t>9263.961875734634</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2084.875383</t>
+          <t>3104.0294</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2084.875383</t>
+          <t>2501.400538</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>80.37697446720975</t>
+          <t>87.63041650479023</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2010,17 +2045,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob-MTr-H2R</t>
+          <t>ALIVE-MoTP-Mob-Uti-ELC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AGRH2R</t>
+          <t>AGRELC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob</t>
+          <t>ALIVE-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2030,7 +2065,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.272093</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2040,27 +2075,27 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>9263.961875734634</t>
+          <t>691.8679257316097</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3104.0294</t>
+          <t>413.4744442</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2501.400538</t>
+          <t>413.4744442</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>87.63041650479023</t>
+          <t>12.933898883882927</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2072,17 +2107,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob-Uti-ELC</t>
+          <t>ALIVE-MoTP-Mob-Uti-H2R</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AGRELC</t>
+          <t>AGRH2R</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob</t>
+          <t>ALIVE-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2092,7 +2127,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2102,22 +2137,22 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>691.8679257316097</t>
+          <t>919.5736092121952</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>413.4744442</t>
+          <t>431.3847446</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>413.4744442</t>
+          <t>408.5523564</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>12.933898883882927</t>
+          <t>16.042381847453658</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2134,17 +2169,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob-Uti-H2R</t>
+          <t>ALIVE-MoTP-Mob-Bike-ELC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AGRH2R</t>
+          <t>AGRELC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob</t>
+          <t>ALIVE-Bike-MoTP-Mob</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2154,37 +2189,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.347826</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>919.5736092121952</t>
+          <t>593.860619456878</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>431.3847446</t>
+          <t>287.0371841</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>408.5523564</t>
+          <t>189.3223981</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>16.042381847453658</t>
+          <t>21.341866006165855</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -2196,17 +2231,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob-Bike-PET</t>
+          <t>AHORT-MoTP-Mob-Trac-ELC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AGRPET</t>
+          <t>AGRELC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob</t>
+          <t>AHORT-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2216,37 +2251,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.386473</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>324.3221308161951</t>
+          <t>13463.450718439024</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>264.0430374</t>
+          <t>5626.288656</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>264.0430374</t>
+          <t>3923.314973</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>42.683732024614635</t>
+          <t>169.93995044468292</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.061644</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -2258,17 +2293,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob-Bike-ELC</t>
+          <t>AHORT-MoTP-Mob-Trac-H2R</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AGRELC</t>
+          <t>AGRH2R</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob</t>
+          <t>AHORT-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2278,7 +2313,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.347826</t>
+          <t>0.241546</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2288,27 +2323,27 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>593.860619456878</t>
+          <t>13268.808765707317</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>287.0371841</t>
+          <t>10005.47449</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>189.3223981</t>
+          <t>2988.072731</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>21.341866006165855</t>
+          <t>68.9840673491122</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.061644</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -2320,7 +2355,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-Trac-ELC</t>
+          <t>AHORT-MoTP-Mob-MTr-ELC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2330,7 +2365,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob</t>
+          <t>AHORT-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2340,37 +2375,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.386473</t>
+          <t>0.43535</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>13463.450718439024</t>
+          <t>8063.7538839102435</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5626.288656</t>
+          <t>2084.875383</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3923.314973</t>
+          <t>2084.875383</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>169.93995044468292</t>
+          <t>80.37697446720975</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0.061644</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -2382,7 +2417,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-Trac-H2R</t>
+          <t>AHORT-MoTP-Mob-MTr-H2R</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2392,7 +2427,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob</t>
+          <t>AHORT-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2402,37 +2437,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.241546</t>
+          <t>0.272093</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>13268.808765707317</t>
+          <t>9263.961875734634</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>10005.47449</t>
+          <t>3104.0294</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2988.072731</t>
+          <t>2501.400538</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>68.9840673491122</t>
+          <t>87.63041650479023</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.061644</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -2444,7 +2479,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-MTr-ELC</t>
+          <t>AHORT-MoTP-Mob-Uti-ELC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2454,7 +2489,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob</t>
+          <t>AHORT-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2464,7 +2499,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.43535</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2474,27 +2509,27 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8063.7538839102435</t>
+          <t>691.8679257316097</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2084.875383</t>
+          <t>413.4744442</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2084.875383</t>
+          <t>413.4744442</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>80.37697446720975</t>
+          <t>12.933898883882927</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -2506,7 +2541,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-MTr-H2R</t>
+          <t>AHORT-MoTP-Mob-Uti-H2R</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2516,7 +2551,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob</t>
+          <t>AHORT-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2526,7 +2561,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.272093</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2536,27 +2571,27 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>9263.961875734634</t>
+          <t>919.5736092121952</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3104.0294</t>
+          <t>431.3847446</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2501.400538</t>
+          <t>408.5523564</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>87.63041650479023</t>
+          <t>16.042381847453658</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -2568,7 +2603,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-Uti-ELC</t>
+          <t>AHORT-MoTP-Stat-Motor-ELC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2578,7 +2613,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob</t>
+          <t>AHORT-MoTP-Stat</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2588,37 +2623,31 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>691.8679257316097</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>413.4744442</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>413.4744442</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>12.933898883882927</t>
-        </is>
+          <t>2947.9024390243903</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v/>
+      </c>
+      <c r="I58" t="n">
+        <v/>
+      </c>
+      <c r="J58" t="n">
+        <v/>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.07416</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -2630,17 +2659,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob-Uti-H2R</t>
+          <t>AINDC-SH-Boiler-WOD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AGRH2R</t>
+          <t>AGRWOD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob</t>
+          <t>AINDC-Boiler-SH</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2650,37 +2679,33 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>919.5736092121952</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>431.3847446</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>408.5523564</t>
-        </is>
+          <t>867.0301290742439</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v/>
+      </c>
+      <c r="I59" t="n">
+        <v/>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>16.042381847453658</t>
+          <t>13.81829268292683</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -2692,7 +2717,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Stat-Motor-ELC</t>
+          <t>AINDC-SH-Boiler-ELC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Stat</t>
+          <t>AINDC-Boiler-SH</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2712,31 +2737,35 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2947.9024390243903</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v/>
-      </c>
-      <c r="I60" t="n">
-        <v/>
+          <t>455.0824390243902</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
       </c>
       <c r="J60" t="n">
         <v/>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0.07416</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -2748,17 +2777,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AINDC-SH-Boiler-WOD</t>
+          <t>AINDC-SH-Boiler-H2R</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AGRWOD</t>
+          <t>AGRH2R</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AINDC-SH</t>
+          <t>AINDC-Boiler-SH</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2768,7 +2797,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2778,7 +2807,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>867.0301290742439</t>
+          <t>214.73626829268292</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -2789,7 +2818,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>13.81829268292683</t>
+          <t>8.131297560975609</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -2806,7 +2835,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AINDC-SH-Boiler-ELC</t>
+          <t>AINDC-SH-HP-ELC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2826,28 +2855,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>455.0824390243902</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>250.0</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>250.0</t>
-        </is>
+          <t>1316.0278740380486</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v/>
+      </c>
+      <c r="I62" t="n">
+        <v/>
       </c>
       <c r="J62" t="n">
         <v/>
@@ -2866,17 +2891,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AINDC-SH-Boiler-H2R</t>
+          <t>AFORE-MoTP-Mob-GB-ELC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AGRH2R</t>
+          <t>AGRELC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AINDC-SH</t>
+          <t>AFORE-GB-MoTP-Mob</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2886,33 +2911,35 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.386473</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>214.73626829268292</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
         <v/>
       </c>
-      <c r="I63" t="n">
-        <v/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6998.669165</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2331.850796</t>
+        </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8.131297560975609</t>
+          <t>23.1234987206439</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.153664</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -2924,17 +2951,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AINDC-SH-HP-ELC</t>
+          <t>AFORE-MoTP-Mob-GB-H2R</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AGRELC</t>
+          <t>AGRH2R</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AINDC-SH</t>
+          <t>AFORE-GB-MoTP-Mob</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2944,31 +2971,35 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>0.241546</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>1316.0278740380486</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
         <v/>
       </c>
-      <c r="I64" t="n">
-        <v/>
-      </c>
-      <c r="J64" t="n">
-        <v/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2440.4418</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>858.7681567</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>56.31941125309268</t>
+        </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.153664</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -2980,7 +3011,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob-GB-ELC</t>
+          <t>AFORE-MoTP-Mob-CY-ELC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2990,7 +3021,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob</t>
+          <t>AFORE-CY-MoTP-Mob</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3013,22 +3044,22 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6998.669165</t>
+          <t>8412.925432</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2331.850796</t>
+          <t>2771.365657</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>23.1234987206439</t>
+          <t>14.624910031219512</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0.153664</t>
+          <t>0.153388</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3040,7 +3071,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob-GB-H2R</t>
+          <t>AFORE-MoTP-Mob-CY-H2R</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3050,7 +3081,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob</t>
+          <t>AFORE-CY-MoTP-Mob</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3073,22 +3104,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2440.4418</t>
+          <t>2742.366674</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>858.7681567</t>
+          <t>1086.065515</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>56.31941125309268</t>
+          <t>35.62031561052683</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0.153664</t>
+          <t>0.153388</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -3100,7 +3131,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob-CY-ELC</t>
+          <t>AFORE-MoTP-Mob-Bike-ELC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3110,7 +3141,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob</t>
+          <t>AFORE-Bike-MoTP-Mob</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3120,154 +3151,40 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.386473</t>
+          <t>0.347826</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>593.860619456878</t>
+        </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8412.925432</t>
+          <t>287.0371841</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2771.365657</t>
+          <t>189.3223981</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>14.624910031219512</t>
+          <t>21.341866006165855</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.153388</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
-        <is>
-          <t>31.536</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>AFORE-MoTP-Mob-CY-H2R</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>AGRH2R</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AFORE-MoTP-Mob</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0.241546</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v/>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>2742.366674</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1086.065515</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>35.62031561052683</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>0.153388</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>31.536</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>AFISH-MoTP-Mob-HYBBoat-DSL</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>AGRDSL</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AFISH-MoTP-Mob</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0.193823</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>1817.8896359951218</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v/>
-      </c>
-      <c r="I69" t="n">
-        <v/>
-      </c>
-      <c r="J69" t="n">
-        <v/>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
         <is>
           <t>31.536</t>
         </is>
